--- a/test/data/bancovde_fixture.xlsx
+++ b/test/data/bancovde_fixture.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3282,6 +3282,164 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Feira de Santana</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Roubo de veículo automotor</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="K84" t="n">
+        <v>58</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>NÃO INFORMADO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Roubo de carga</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="K85" t="n">
+        <v>41</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NÃO INFORMADO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Roubo de carga</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="K86" t="n">
+        <v>42</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Recife</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Estupro de vulnerável</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="H87" t="n">
+        <v>9</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>10</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Recife</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Mortes no trânsito</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="H88" t="n">
+        <v>4</v>
+      </c>
+      <c r="I88" t="n">
+        <v>14</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>18</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
